--- a/samples/Trial_Balance_VS_Aug-26.xlsx
+++ b/samples/Trial_Balance_VS_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>63699.47</v>
+        <v>5123.03</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>182.28</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>59359.94</v>
+        <v>55958.46</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>3519.31</v>
+        <v>3741.17</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>3176.52</v>
+        <v>2939.04</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>6885.51</v>
+        <v>6880.41</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>16200</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>29892.84</v>
+        <v>29000.68</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D15">
-        <v>-11375.81</v>
+        <v>-10723.94</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>1802.68</v>
+        <v>1801.35</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D17">
-        <v>-17318.83</v>
+        <v>-16481.91</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-9218.95</v>
+        <v>-8451.49</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-5084.45</v>
+        <v>-4064.55</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-3397.44</v>
+        <v>-3264.35</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D21">
-        <v>-8383.5</v>
+        <v>-7182.84</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-71229.38</v>
+        <v>-40000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-38026.8</v>
+        <v>-8000</v>
       </c>
     </row>
     <row r="24">
@@ -688,7 +688,7 @@
         <v>Equity</v>
       </c>
       <c r="D24">
-        <v>-19533.76</v>
+        <v>-19519.29</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-179438.02</v>
+        <v>-143444.08</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-1128.92</v>
+        <v>-902.47</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>65045.18</v>
+        <v>51997.6</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>56044.05</v>
+        <v>44802.03</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>5213.09</v>
+        <v>4167.38</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>7360.37</v>
+        <v>5883.93</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>5729.06</v>
+        <v>4579.86</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>9409.72</v>
+        <v>7522.2</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>3142.83</v>
+        <v>2512.4</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>20587.5</v>
+        <v>16255.48</v>
       </c>
     </row>
     <row r="35">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>6885.51</v>
+        <v>5504.32</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_VS_Aug-26.xlsx
+++ b/samples/Trial_Balance_VS_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>5123.03</v>
+        <v>31901.68</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>13200</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="14">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-40000</v>
+        <v>-70000</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         <v>Equity</v>
       </c>
       <c r="D24">
-        <v>-19519.29</v>
+        <v>-22719.29</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-143444.08</v>
+        <v>-51236.74</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-902.47</v>
+        <v>-237.49</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>51997.6</v>
+        <v>12975.72</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>44802.03</v>
+        <v>11212.33</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>4167.38</v>
+        <v>1041.85</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>5883.93</v>
+        <v>1470.98</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>4579.86</v>
+        <v>1133.16</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>7522.2</v>
+        <v>1892.38</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>2512.4</v>
+        <v>616.25</v>
       </c>
     </row>
     <row r="34">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>5504.32</v>
+        <v>1376.08</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_VS_Aug-26.xlsx
+++ b/samples/Trial_Balance_VS_Aug-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>31901.68</v>
+        <v>1878.82</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +688,7 @@
         <v>Equity</v>
       </c>
       <c r="D24">
-        <v>-22719.29</v>
+        <v>-8095.85</v>
       </c>
     </row>
     <row r="25">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-51236.74</v>
+        <v>-35837.32</v>
       </c>
     </row>
     <row r="26">
